--- a/backtest_runs/20260410_193731/by_symbol/ASTM/ASTM.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/ASTM/ASTM.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>100000</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>100000</v>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>100000</v>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>100000</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>100000</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>100000</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>100000</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>100000</v>
